--- a/data/trans_dic/P21D_3_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P21D_3_R-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando medicamentos, no los pudo comprar por motivos económicos</t>
+          <t>Población que, necesitando medicamentos, no los pudo comprar por motivos económicos (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,15</t>
+          <t>0,0; 1,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,74</t>
+          <t>0,0; 0,76</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,36</t>
+          <t>0,0; 0,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,46</t>
+          <t>0,0; 0,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,25</t>
+          <t>0,0; 0,26</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,25</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,36</t>
+          <t>0,03; 0,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando medicamentos, no los pudo comprar por motivos económicos</t>
+          <t>Población que, necesitando medicamentos, no los pudo comprar por motivos económicos (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1472</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3880</t>
+          <t>0; 4541</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4227</t>
+          <t>0; 4301</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3981</t>
+          <t>0; 3943</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4343</t>
+          <t>0; 3427</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5225</t>
+          <t>0; 5274</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1866</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1350</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1569</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4532</t>
+          <t>0; 4554</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>557; 5711</t>
+          <t>552; 5636</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>772; 7164</t>
+          <t>761; 6990</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21D_3_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P21D_3_R-Estudios-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,34</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,76</t>
+          <t>0,0; 0,75</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,35</t>
+          <t>0,0; 0,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,37</t>
+          <t>0,0; 0,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,26</t>
+          <t>0,0; 0,27</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,27</t>
+          <t>0,0; 0,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,36</t>
+          <t>0,03; 0,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,22</t>
+          <t>0,02; 0,2</t>
         </is>
       </c>
     </row>
@@ -861,12 +861,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1264</t>
         </is>
       </c>
     </row>
@@ -884,12 +884,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4541</t>
+          <t>0; 4330</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4301</t>
+          <t>0; 4665</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>749</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>1496</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3943</t>
+          <t>0; 3825</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3427</t>
+          <t>0; 3739</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5274</t>
+          <t>0; 5328</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>2759</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4554</t>
+          <t>0; 3780</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>552; 5636</t>
+          <t>561; 5538</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>761; 6990</t>
+          <t>701; 6393</t>
         </is>
       </c>
     </row>
